--- a/04_Figures/F04_association/modules/training/wilcoxon/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/training/wilcoxon/c_data/results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -64,12 +64,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -468,14 +462,14 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.051645108243261</v>
+        <v>0.107408881226421</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>0.94971694971695</v>
+        <v>0.228438228438228</v>
       </c>
       <c r="G2" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="3">
@@ -489,11 +483,11 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0490807844388881</v>
+        <v>0.0500207654019837</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.344988344988345</v>
+        <v>0.754578754578755</v>
       </c>
       <c r="G3" t="n">
         <v>0.94971694971695</v>
@@ -510,14 +504,14 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0398755144245484</v>
+        <v>0.039177920426858</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>0.94971694971695</v>
+        <v>0.490842490842491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="5">
@@ -531,14 +525,14 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0628357970706258</v>
+        <v>-0.208650121301236</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="n">
-        <v>0.572760572760573</v>
+        <v>0.413586413586414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="6">
@@ -552,14 +546,14 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0625604836024491</v>
+        <v>0.0726297388149487</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
-        <v>0.282384282384282</v>
+        <v>0.344988344988345</v>
       </c>
       <c r="G6" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +567,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0420935136632633</v>
+        <v>0.0537246405350849</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="n">
@@ -594,11 +588,11 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.151601830472101</v>
+        <v>-0.00248676485854419</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="n">
-        <v>0.344988344988345</v>
+        <v>0.851814851814852</v>
       </c>
       <c r="G8" t="n">
         <v>0.94971694971695</v>
@@ -615,14 +609,14 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0219681623428629</v>
+        <v>0.165217397369462</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="n">
-        <v>0.754578754578755</v>
+        <v>0.413586413586414</v>
       </c>
       <c r="G9" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="10">
@@ -636,11 +630,11 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.210337548971022</v>
+        <v>-0.017279819352333</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="n">
-        <v>0.282384282384282</v>
+        <v>0.94971694971695</v>
       </c>
       <c r="G10" t="n">
         <v>0.94971694971695</v>
@@ -657,14 +651,14 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0275644645102259</v>
+        <v>-0.0988788595672188</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="n">
-        <v>0.94971694971695</v>
+        <v>0.413586413586414</v>
       </c>
       <c r="G11" t="n">
-        <v>0.94971694971695</v>
+        <v>0.8998778998779</v>
       </c>
     </row>
     <row r="12">
@@ -678,55 +672,13 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0650558953349124</v>
+        <v>0.024840394646423</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="n">
-        <v>0.490842490842491</v>
+        <v>0.851814851814852</v>
       </c>
       <c r="G12" t="n">
-        <v>0.94971694971695</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.100532186404756</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="n">
-        <v>0.413586413586414</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.94971694971695</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0258182073451675</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14" t="n">
-        <v>0.754578754578755</v>
-      </c>
-      <c r="G14" t="n">
         <v>0.94971694971695</v>
       </c>
     </row>
@@ -743,45 +695,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -790,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.051645108243261</v>
+        <v>0.0537246405350849</v>
       </c>
     </row>
   </sheetData>
